--- a/output/pdf_financials_xlsx/GGAU.xlsx
+++ b/output/pdf_financials_xlsx/GGAU.xlsx
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.339399</v>
+        <v>-0.339399</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.19887</v>
+        <v>-1.19887</v>
       </c>
     </row>
     <row r="17">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.339399</v>
+        <v>-0.339399</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.19887</v>
+        <v>-1.19887</v>
       </c>
     </row>
     <row r="21">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.339399</v>
+        <v>-0.339399</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.19887</v>
+        <v>-1.19887</v>
       </c>
     </row>
     <row r="24">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-21.212438</v>
+        <v>21.212438</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-30.740256</v>
+        <v>30.740256</v>
       </c>
     </row>
     <row r="27">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.339399</v>
+        <v>-0.339399</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.19887</v>
+        <v>-1.19887</v>
       </c>
     </row>
     <row r="28">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.339399</v>
+        <v>-0.339399</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.19887</v>
+        <v>-1.19887</v>
       </c>
     </row>
     <row r="30">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.048528</v>
       </c>
     </row>
     <row r="93">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.010298</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.176259</v>
       </c>
     </row>
     <row r="119">
@@ -2538,7 +2538,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3008,7 +3012,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>-0.010298</v>
       </c>
@@ -3648,10 +3656,10 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.339399</v>
+        <v>-0.339399</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>1.19887</v>
+        <v>-1.19887</v>
       </c>
     </row>
     <row r="52">

--- a/output/pdf_financials_xlsx/GGAU.xlsx
+++ b/output/pdf_financials_xlsx/GGAU.xlsx
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.029326</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.021297</v>
       </c>
     </row>
     <row r="35">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.029326</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.021297</v>
       </c>
     </row>
     <row r="37">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.048333</v>
+        <v>0.019007</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.021297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
